--- a/data/dataset/tables/наконечники стрел.xlsx
+++ b/data/dataset/tables/наконечники стрел.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15600" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="наконечники стрел" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="наконечники стрел" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.140625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -481,24 +481,19 @@
           <t>сечение</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>ребра</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>уд85_1-2_а.jpg</t>
+          <t>уд85_1-11_а.jpg</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>наконечник копья</t>
+          <t>наконечники стрел</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -508,47 +503,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>втулочный</t>
+          <t>втульчатый</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>не нужно</t>
+          <t>объемное</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>уд85_1-2_б.jpg</t>
+          <t>уд85_1-11_б.jpg</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>наконечник копья</t>
+          <t>наконечники стрел</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -558,47 +543,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>втулочный</t>
+          <t>втульчатый</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>не нужно</t>
+          <t>объемное</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>уд85_1-2_в.jpg</t>
+          <t>уд85_1-11_в.jpg</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>наконечник копья</t>
+          <t>наконечники стрел</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -608,47 +583,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>втулочный</t>
+          <t>втульчатый</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>не нужно</t>
+          <t>объемное</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>уд85_1-2_г.jpg</t>
+          <t>уд85_1-12_а.jpg</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>наконечник копья</t>
+          <t>наконечники стрел</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -658,47 +623,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>втулочный</t>
+          <t>черешковый</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>не нужно</t>
+          <t>объемное</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>уд85_1-2_д.jpg</t>
+          <t>уд85_1-12_б.jpg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>наконечник копья</t>
+          <t>наконечники стрел</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -708,42 +663,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>втулочный</t>
+          <t>черешковый</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>не нужно</t>
+          <t>объемное</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>уд85_1-11_а.jpg</t>
+          <t>уд85_1-12_в.jpg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -758,37 +703,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>втульчатый</t>
+          <t>черешковый</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>пулевидный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>да</t>
+          <t>объемное</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>уд85_1-11_б.jpg</t>
+          <t>уд85_1-12_г.jpg</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -803,37 +743,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>втульчатый</t>
+          <t>черешковый</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>пулевидный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>да</t>
+          <t>объемное</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>уд85_1-11_в.jpg</t>
+          <t>уд85_1-20_а.jpg</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -843,42 +778,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>бронза</t>
+          <t>железо</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>втульчатый</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>пулевидный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>да</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>уд85_1-12_а.jpg</t>
+          <t>уд85_1-20_б.jpg</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -888,42 +818,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>бронза</t>
+          <t>железо</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>расщепленный насад</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>шипастый</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>да</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>уд85_1-12_б.jpg</t>
+          <t>уд85_1-20_в.jpg</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -933,42 +858,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>бронза</t>
+          <t>железо</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>расщепленный насад</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>шипастый</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>да</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>уд85_1-12_в.jpg</t>
+          <t>уд85_4-12_а.jpg</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -978,42 +898,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>бронза</t>
+          <t>железо</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>расщепленный насад</t>
+          <t>черешковый</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>шипастый</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>да</t>
+          <t>объемное</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>уд85_1-12_г.jpg</t>
+          <t>уд85_4-12_б.jpg</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1023,42 +938,37 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>бронза</t>
+          <t>железо</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>расщепленный насад</t>
+          <t>черешковый</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>шипастый</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>да</t>
+          <t>объемное</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>уд85_1-20_а.jpg</t>
+          <t>уд85_4-15_а.jpg</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1073,37 +983,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>черешковый</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>треугольный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>уд85_1-20_б.jpg</t>
+          <t>уд85_4-15_б.jpg</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1118,37 +1023,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>черешковый</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>треугольный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>уд85_1-20_в.jpg</t>
+          <t>уд85_4-15_в.jpg</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1163,37 +1063,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>черешковый</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>треугольный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>уд85_4-12_а.jpg</t>
+          <t>уд85_8-7_а.jpg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1203,12 +1098,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>железо</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1218,27 +1113,22 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>трапециевидный</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>да</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>уд85_4-12_б.jpg</t>
+          <t>уд85_8-7_б.jpg</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1248,12 +1138,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>железо</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1263,27 +1153,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>трапециевидный</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>да</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>уд85_4-15_а.jpg</t>
+          <t>уд85_8-7_в.jpg</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1293,12 +1178,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>железо</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1308,27 +1193,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>трапециевидный</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>уд85_4-15_б.jpg</t>
+          <t>уд85_8-7_г.jpg</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1338,12 +1218,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>железо</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1353,27 +1233,22 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>трапециевидный</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>68</v>
+        <v>503</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>уд85_4-15_в.jpg</t>
+          <t>уд85_12-28_а.jpg</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1383,42 +1258,37 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>железо</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>черешковый</t>
+          <t>втульчатый</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>трапециевидный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>объемное</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>69</v>
+        <v>504</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>уд85_8-7_а.jpg</t>
+          <t>уд85_12-28_б.jpg</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1428,42 +1298,37 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>черешковый</t>
+          <t>втульчатый</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>объемное</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>70</v>
+        <v>505</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>уд85_8-7_б.jpg</t>
+          <t>уд85_12-28_в.jpg</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1473,42 +1338,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>черешковый</t>
+          <t>втульчатый</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>объемное</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>71</v>
+        <v>506</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>уд85_8-7_в.jpg</t>
+          <t>уд85_12-32_а.jpg</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1518,42 +1378,37 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>черешковый</t>
+          <t>втульчатый</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>72</v>
+        <v>507</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>уд85_8-7_г.jpg</t>
+          <t>уд85_12-32_б.jpg</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1563,177 +1418,157 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>черешковый</t>
+          <t>втульчатый</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>уд85_12-16_а.jpg</t>
+          <t>уд85_12-32_в.jpg</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>копье</t>
+          <t>наконечники стрел</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>расщепленный насад</t>
+          <t>втульчатый</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>двухлопастной</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>да</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>уд85_12-16_б.jpg</t>
+          <t>уд85_12-32_г.jpg</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>копье</t>
+          <t>наконечники стрел</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>расщепленный насад</t>
+          <t>втульчатый</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>двухлопастной</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>да</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>уд85_12-16_в.jpg</t>
+          <t>уд85_12-33_а.jpg</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>копье</t>
+          <t>наконечники стрел</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>расщепленный насад</t>
+          <t>черешковый</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>двухлопастной</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>да</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>уд85_12-28_а.jpg</t>
+          <t>уд85_12-33_б.jpg</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1743,42 +1578,37 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>втульчатый</t>
+          <t>черешковый</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>да</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>уд85_12-28_б.jpg</t>
+          <t>уд85_12-33_в.jpg</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1788,42 +1618,37 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>втульчатый</t>
+          <t>черешковый</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>да</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>уд85_12-28_в.jpg</t>
+          <t>уд85_13-1_а.jpg</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1833,42 +1658,37 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>железо</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>втульчатый</t>
+          <t>черешковый</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>да</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>уд85_12-32_а.jpg</t>
+          <t>уд85_13-1_б.jpg</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1878,42 +1698,37 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>железо</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>втульчатый</t>
+          <t>черешковый</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>четырехгранный</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>уд85_12-32_б.jpg</t>
+          <t>уд85_13-1_в.jpg</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1923,42 +1738,37 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>железо</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>втульчатый</t>
+          <t>черешковый</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>четырехгранный</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>уд85_12-32_в.jpg</t>
+          <t>уд85_13-1_г.jpg</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1968,42 +1778,37 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>железо</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>втульчатый</t>
+          <t>черешковый</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>четырехгранный</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>уд85_12-32_г.jpg</t>
+          <t>уд85_13-2_а.jpg</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2013,42 +1818,37 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>железо</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>втульчатый</t>
+          <t>черешковый</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>четырехгранный</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>уд85_12-33_а.jpg</t>
+          <t>уд85_13-2_б.jpg</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2058,12 +1858,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>железо</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2073,27 +1873,22 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>уд85_12-33_б.jpg</t>
+          <t>уд85_13-2_в.jpg</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2103,12 +1898,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>железо</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2118,27 +1913,22 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>уд85_12-33_в.jpg</t>
+          <t>уд85_13-2_г.jpg</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2148,12 +1938,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>железо</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2163,27 +1953,22 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>уд85_13-1_а.jpg</t>
+          <t>уд85_13-3_а.jpg</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2198,7 +1983,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2208,27 +1993,22 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>уд85_13-1_б.jpg</t>
+          <t>уд85_13-3_б.jpg</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2243,7 +2023,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2253,27 +2033,22 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>уд85_13-1_в.jpg</t>
+          <t>уд85_13-3_в.jpg</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2288,7 +2063,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2298,27 +2073,22 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>уд85_13-1_г.jpg</t>
+          <t>уд85_13-3_г.jpg</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2333,7 +2103,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2343,27 +2113,22 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>уд85_13-2_а.jpg</t>
+          <t>уд85_13-4_а.jpg</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2378,7 +2143,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2388,27 +2153,22 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>уд85_13-2_б.jpg</t>
+          <t>уд85_13-4_б.jpg</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2423,7 +2183,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2433,27 +2193,22 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>уд85_13-2_в.jpg</t>
+          <t>уд85_13-4_в.jpg</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2468,7 +2223,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2478,27 +2233,22 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>уд85_13-2_г.jpg</t>
+          <t>уд85_13-4_г.jpg</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2513,7 +2263,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2523,27 +2273,22 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>уд85_13-3_а.jpg</t>
+          <t>уд85_13-5_а.jpg</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2558,7 +2303,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2568,27 +2313,22 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>уд85_13-3_б.jpg</t>
+          <t>уд85_13-5_б.jpg</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2603,7 +2343,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2613,27 +2353,22 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>уд85_13-3_в.jpg</t>
+          <t>уд85_13-5_в.jpg</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2648,7 +2383,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2658,27 +2393,22 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>уд85_13-3_г.jpg</t>
+          <t>уд85_13-5_г.jpg</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2693,7 +2423,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2703,27 +2433,22 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>уд85_13-4_а.jpg</t>
+          <t>уд85_13-6_а.jpg</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2738,7 +2463,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2748,27 +2473,22 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>уд85_13-4_б.jpg</t>
+          <t>уд85_13-6_б.jpg</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2783,7 +2503,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2793,27 +2513,22 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>уд85_13-4_в.jpg</t>
+          <t>уд85_13-6_в.jpg</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2828,7 +2543,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2838,27 +2553,22 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>уд85_13-4_г.jpg</t>
+          <t>уд85_13-6_г.jpg</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2873,7 +2583,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2883,27 +2593,22 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>уд85_13-5_а.jpg</t>
+          <t>уд85_13-7_а.jpg</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2918,7 +2623,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2928,27 +2633,22 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>уд85_13-5_б.jpg</t>
+          <t>уд85_13-7_б.jpg</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2963,7 +2663,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2973,27 +2673,22 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>уд85_13-5_в.jpg</t>
+          <t>уд85_13-7_в.jpg</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3008,7 +2703,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3018,27 +2713,22 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>уд85_13-5_г.jpg</t>
+          <t>уд85_13-7_г.jpg</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3053,7 +2743,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3063,27 +2753,22 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>уд85_13-6_а.jpg</t>
+          <t>уд85_13-8_а.jpg</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3098,7 +2783,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3108,27 +2793,22 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>объемное</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>уд85_13-6_б.jpg</t>
+          <t>уд85_13-8_б.jpg</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3143,7 +2823,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3153,27 +2833,22 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>объемное</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>уд85_13-6_в.jpg</t>
+          <t>уд85_13-8_в.jpg</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3188,7 +2863,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3198,27 +2873,22 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>объемное</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>уд85_13-6_г.jpg</t>
+          <t>уд85_13-9_а.jpg</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3233,7 +2903,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3243,27 +2913,22 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>объемное</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>уд85_13-7_а.jpg</t>
+          <t>уд85_13-9_б.jpg</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3278,7 +2943,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3288,27 +2953,22 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>объемное</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>уд85_13-7_б.jpg</t>
+          <t>уд85_13-9_в.jpg</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3323,7 +2983,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3333,27 +2993,22 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>объемное</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>уд85_13-7_в.jpg</t>
+          <t>уд85_13-10_а.jpg</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3368,7 +3023,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3378,27 +3033,22 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>уд85_13-7_г.jpg</t>
+          <t>уд85_13-10_б.jpg</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3413,7 +3063,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3423,27 +3073,22 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>трехлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>уд85_13-8_а.jpg</t>
+          <t>уд85_13-10_в.jpg</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3458,7 +3103,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3468,27 +3113,22 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>двухлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>да</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>уд85_13-8_б.jpg</t>
+          <t>уд85_13-11_а.jpg</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3503,7 +3143,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3513,27 +3153,22 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>треугольный</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>да</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>уд85_13-8_в.jpg</t>
+          <t>уд85_13-11_б.jpg</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3548,7 +3183,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3558,27 +3193,22 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>треугольный</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>да</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>уд85_13-9_а.jpg</t>
+          <t>уд85_13-11_в.jpg</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3593,7 +3223,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3603,27 +3233,22 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>двухлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>да</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>уд85_13-9_б.jpg</t>
+          <t>уд85_13-12_а.jpg</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3638,7 +3263,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3648,27 +3273,22 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>двухлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>да</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>уд85_13-9_в.jpg</t>
+          <t>уд85_13-12_б.jpg</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3683,7 +3303,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3693,27 +3313,22 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>двухлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>да</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>уд85_13-10_а.jpg</t>
+          <t>уд85_13-12_в.jpg</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3728,7 +3343,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3738,27 +3353,22 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>двухлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>уд85_13-10_б.jpg</t>
+          <t>уд85_13-13_а.jpg</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3773,7 +3383,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3783,27 +3393,22 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>двухлопастной</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>уд85_13-10_в.jpg</t>
+          <t>уд85_13-13_б.jpg</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3818,7 +3423,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3828,27 +3433,22 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>двухлопастной</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>уд85_13-11_а.jpg</t>
+          <t>уд85_13-13_в.jpg</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3863,7 +3463,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3873,27 +3473,22 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>двухлопастной</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>уд85_13-11_б.jpg</t>
+          <t>уд85_13-14_а.jpg</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3908,7 +3503,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3918,27 +3513,22 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>двухлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>уд85_13-11_в.jpg</t>
+          <t>уд85_13-14_б.jpg</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3953,7 +3543,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3963,27 +3553,22 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>двухлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ромбовидное</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>уд85_13-12_а.jpg</t>
+          <t>уд85_13-14_в.jpg</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3998,7 +3583,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4008,27 +3593,22 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>двухлопастной</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>уд85_13-12_б.jpg</t>
+          <t>уд85_13-15_а.jpg</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4043,7 +3623,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4053,27 +3633,22 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>двухлопастной</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>уд85_13-12_в.jpg</t>
+          <t>уд85_13-15_б.jpg</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4088,7 +3663,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4098,27 +3673,22 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>двухлопастной</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>уд85_13-13_а.jpg</t>
+          <t>уд85_13-15_в.jpg</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4133,7 +3703,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4143,27 +3713,22 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>прямоугольный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>уд85_13-13_б.jpg</t>
+          <t>уд85_13-16_а.jpg</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4178,7 +3743,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4188,27 +3753,22 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>прямоугольный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>уд85_13-13_в.jpg</t>
+          <t>уд85_13-16_б.jpg</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4223,7 +3783,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4233,27 +3793,22 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>прямоугольный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>уд85_13-14_а.jpg</t>
+          <t>уд85_13-16_в.jpg</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4268,7 +3823,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4278,27 +3833,22 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>вильчатый</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>уд85_13-14_б.jpg</t>
+          <t>уд85_13-17_а.jpg</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4313,7 +3863,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4323,27 +3873,22 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>вильчатый</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>уд85_13-14_в.jpg</t>
+          <t>уд85_13-17_б.jpg</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4358,7 +3903,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4368,27 +3913,22 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>вильчатый</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>уд85_13-15_а.jpg</t>
+          <t>уд85_13-17_в.jpg</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4403,7 +3943,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4413,27 +3953,22 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>уд85_13-15_б.jpg</t>
+          <t>уд85_13-18_а.jpg</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4448,7 +3983,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4458,27 +3993,22 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>уд85_13-15_в.jpg</t>
+          <t>уд85_13-18_б.jpg</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4493,7 +4023,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4503,27 +4033,22 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>уд85_13-16_а.jpg</t>
+          <t>уд85_13-18_в.jpg</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4538,7 +4063,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4548,27 +4073,22 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>уд85_13-16_б.jpg</t>
+          <t>уд85_13-19_а.jpg</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4583,7 +4103,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4593,27 +4113,22 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>уд85_13-16_в.jpg</t>
+          <t>уд85_13-19_б.jpg</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4628,7 +4143,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4638,27 +4153,22 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>уд85_13-17_а.jpg</t>
+          <t>уд85_13-19_в.jpg</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4673,7 +4183,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4683,27 +4193,22 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>уд85_13-17_б.jpg</t>
+          <t>уд85_13-20_а.jpg</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4718,7 +4223,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4728,27 +4233,22 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>уд85_13-17_в.jpg</t>
+          <t>уд85_13-20_б.jpg</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4763,7 +4263,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4773,27 +4273,22 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>уд85_13-18_а.jpg</t>
+          <t>уд85_13-20_в.jpg</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4808,7 +4303,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4818,27 +4313,22 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>уд85_13-18_б.jpg</t>
+          <t>уд85_13-21_а.jpg</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4853,7 +4343,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4863,27 +4353,22 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>уд85_13-18_в.jpg</t>
+          <t>уд85_13-21_б.jpg</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4898,7 +4383,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4908,27 +4393,22 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>уд85_13-19_а.jpg</t>
+          <t>уд85_13-21_в.jpg</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4943,7 +4423,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4953,27 +4433,22 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>заостренный</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>уд85_13-19_б.jpg</t>
+          <t>уд85_13-22_а.jpg</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4988,7 +4463,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4998,27 +4473,22 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>уд85_13-19_в.jpg</t>
+          <t>уд85_13-22_б.jpg</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5033,7 +4503,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5043,27 +4513,22 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>уд85_13-20_а.jpg</t>
+          <t>уд85_13-22_в.jpg</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5078,7 +4543,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5088,27 +4553,22 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>578</v>
+        <v>600</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>уд85_13-20_б.jpg</t>
+          <t>уд85_14-11_а.jpg</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5123,7 +4583,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5133,27 +4593,22 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>579</v>
+        <v>601</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>уд85_13-20_в.jpg</t>
+          <t>уд85_14-11_б.jpg</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5168,7 +4623,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5178,27 +4633,22 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>ромбовидный</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>580</v>
+        <v>602</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>уд85_13-21_а.jpg</t>
+          <t>уд85_14-11_в.jpg</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5213,7 +4663,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5223,27 +4673,22 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>треугольный</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>581</v>
+        <v>603</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>уд85_13-21_б.jpg</t>
+          <t>уд85_14-11_г.jpg</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5258,7 +4703,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5268,377 +4713,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>треугольный</t>
+          <t>расщепленный</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>582</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>уд85_13-21_в.jpg</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>наконечники стрел</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>железо</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Целый</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>черешковый</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>треугольный</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>583</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>уд85_13-22_а.jpg</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>наконечники стрел</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>железо</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Целый</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>черешковый</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>подквадратный</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>584</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>уд85_13-22_б.jpg</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>наконечники стрел</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>железо</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Целый</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>черешковый</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>подквадратный</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>585</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>уд85_13-22_в.jpg</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>наконечники стрел</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>железо</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Целый</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>черешковый</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>подквадратный</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>плоский</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>600</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>уд85_14-11_а.jpg</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>наконечники стрел</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>железо</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Фрагмент</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>черешковый</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>трехлопастной</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>601</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>уд85_14-11_б.jpg</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>наконечники стрел</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>железо</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Фрагмент</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>черешковый</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>трехлопастной</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>602</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>уд85_14-11_в.jpg</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>наконечники стрел</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>железо</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Фрагмент</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>черешковый</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>трехлопастной</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>603</v>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>уд85_14-11_г.jpg</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>наконечники стрел</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>железо</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Фрагмент</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>черешковый</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>трехлопастной</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>нет</t>
+          <t>плоское</t>
         </is>
       </c>
     </row>
